--- a/www/terminologies/CodeSystem-TRE-R16-LieuFormation.xlsx
+++ b/www/terminologies/CodeSystem-TRE-R16-LieuFormation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4151" uniqueCount="2783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4154" uniqueCount="2785">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1360</t>
+    <t>1361</t>
   </si>
   <si>
     <t>Code</t>
@@ -2438,6 +2438,12 @@
   </si>
   <si>
     <t>IFSI de l'Hôpital Saint-Lazare</t>
+  </si>
+  <si>
+    <t>UI340</t>
+  </si>
+  <si>
+    <t>IFSI de l'Hôpital de Mont-Saint-Martin</t>
   </si>
   <si>
     <t>UK1</t>
@@ -8778,7 +8784,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1361"/>
+  <dimension ref="A1:D1362"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -14157,21 +14163,21 @@
       <c r="C448" t="s" s="2">
         <v>955</v>
       </c>
-      <c r="D448" t="s" s="2">
-        <v>956</v>
-      </c>
+      <c r="D448" s="2"/>
     </row>
     <row r="449">
       <c r="A449" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B449" t="s" s="2">
+        <v>956</v>
+      </c>
+      <c r="C449" t="s" s="2">
         <v>957</v>
       </c>
-      <c r="C449" t="s" s="2">
+      <c r="D449" t="s" s="2">
         <v>958</v>
       </c>
-      <c r="D449" s="2"/>
     </row>
     <row r="450">
       <c r="A450" t="s" s="2">
@@ -14195,21 +14201,21 @@
       <c r="C451" t="s" s="2">
         <v>962</v>
       </c>
-      <c r="D451" t="s" s="2">
-        <v>963</v>
-      </c>
+      <c r="D451" s="2"/>
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B452" t="s" s="2">
+        <v>963</v>
+      </c>
+      <c r="C452" t="s" s="2">
         <v>964</v>
       </c>
-      <c r="C452" t="s" s="2">
+      <c r="D452" t="s" s="2">
         <v>965</v>
       </c>
-      <c r="D452" s="2"/>
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
@@ -18395,7 +18401,7 @@
         <v>1662</v>
       </c>
       <c r="C801" t="s" s="2">
-        <v>1657</v>
+        <v>1663</v>
       </c>
       <c r="D801" s="2"/>
     </row>
@@ -18404,10 +18410,10 @@
         <v>61</v>
       </c>
       <c r="B802" t="s" s="2">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="C802" t="s" s="2">
-        <v>1664</v>
+        <v>1659</v>
       </c>
       <c r="D802" s="2"/>
     </row>
@@ -18709,21 +18715,21 @@
       <c r="C827" t="s" s="2">
         <v>1714</v>
       </c>
-      <c r="D827" t="s" s="2">
-        <v>1715</v>
-      </c>
+      <c r="D827" s="2"/>
     </row>
     <row r="828">
       <c r="A828" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B828" t="s" s="2">
+        <v>1715</v>
+      </c>
+      <c r="C828" t="s" s="2">
         <v>1716</v>
       </c>
-      <c r="C828" t="s" s="2">
+      <c r="D828" t="s" s="2">
         <v>1717</v>
       </c>
-      <c r="D828" s="2"/>
     </row>
     <row r="829">
       <c r="A829" t="s" s="2">
@@ -24637,7 +24643,7 @@
         <v>2702</v>
       </c>
       <c r="C1321" t="s" s="2">
-        <v>1603</v>
+        <v>2703</v>
       </c>
       <c r="D1321" s="2"/>
     </row>
@@ -24646,10 +24652,10 @@
         <v>61</v>
       </c>
       <c r="B1322" t="s" s="2">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="C1322" t="s" s="2">
-        <v>2704</v>
+        <v>1605</v>
       </c>
       <c r="D1322" s="2"/>
     </row>
@@ -25120,6 +25126,18 @@
         <v>2782</v>
       </c>
       <c r="D1361" s="2"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B1362" t="s" s="2">
+        <v>2783</v>
+      </c>
+      <c r="C1362" t="s" s="2">
+        <v>2784</v>
+      </c>
+      <c r="D1362" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
